--- a/project/outputs_xlsx_solution/test_new1.2-wide.xlsx
+++ b/project/outputs_xlsx_solution/test_new1.2-wide.xlsx
@@ -65,16 +65,22 @@
     <t>addi X1, X1, -1</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
   </si>
   <si>
     <t>bne X1, X0, 8</t>
   </si>
   <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
-    <t>EX</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>IS</t>
   </si>
   <si>
     <t>[Legend]</t>
@@ -86,13 +92,37 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -537,7 +567,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -557,13 +587,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -583,13 +613,13 @@
         <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -609,13 +639,16 @@
         <v>7</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -626,7 +659,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -635,13 +668,13 @@
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -664,7 +697,7 @@
         <v>10</v>
       </c>
       <c r="N7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -684,47 +717,50 @@
         <v>7</v>
       </c>
       <c r="M8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="L9" t="s">
+        <v>5</v>
       </c>
       <c r="M9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N9" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O9" t="s">
         <v>10</v>
       </c>
       <c r="P9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M10" t="s">
         <v>5</v>
@@ -736,64 +772,64 @@
         <v>10</v>
       </c>
       <c r="P10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="M11" t="s">
+        <v>5</v>
+      </c>
+      <c r="N11" t="s">
+        <v>7</v>
       </c>
       <c r="O11" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>10</v>
-      </c>
-      <c r="R11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="N12" t="s">
+        <v>5</v>
       </c>
       <c r="O12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P12" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="s">
         <v>10</v>
       </c>
       <c r="R12" t="s">
-        <v>13</v>
-      </c>
-      <c r="S12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>8</v>
@@ -801,22 +837,22 @@
       <c r="C13" t="s">
         <v>8</v>
       </c>
+      <c r="O13" t="s">
+        <v>5</v>
+      </c>
+      <c r="P13" t="s">
+        <v>7</v>
+      </c>
       <c r="Q13" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R13" t="s">
-        <v>7</v>
-      </c>
-      <c r="S13" t="s">
-        <v>10</v>
-      </c>
-      <c r="T13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>12</v>
@@ -824,91 +860,206 @@
       <c r="C14" t="s">
         <v>9</v>
       </c>
+      <c r="O14" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" t="s">
+        <v>7</v>
+      </c>
       <c r="Q14" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S14" t="s">
-        <v>10</v>
-      </c>
-      <c r="T14" t="s">
-        <v>13</v>
-      </c>
-      <c r="U14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>16</v>
       </c>
       <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="P15" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>7</v>
+      </c>
+      <c r="R15" t="s">
+        <v>15</v>
+      </c>
+      <c r="S15" t="s">
+        <v>10</v>
+      </c>
+      <c r="T15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R16" t="s">
+        <v>7</v>
+      </c>
+      <c r="S16" t="s">
+        <v>10</v>
+      </c>
+      <c r="T16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" t="s">
+        <v>7</v>
+      </c>
+      <c r="S17" t="s">
         <v>11</v>
       </c>
-      <c r="R15" t="s">
-        <v>5</v>
-      </c>
-      <c r="S15" t="s">
-        <v>7</v>
-      </c>
-      <c r="T15" t="s">
-        <v>10</v>
-      </c>
-      <c r="U15" t="s">
-        <v>13</v>
-      </c>
-      <c r="V15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
+      <c r="T17" t="s">
+        <v>10</v>
+      </c>
+      <c r="U17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="R18" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" t="s">
+        <v>7</v>
+      </c>
+      <c r="T18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
+      <c r="U18" t="s">
+        <v>10</v>
+      </c>
+      <c r="V18" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
